--- a/2-data/tracking_start_times.xlsx
+++ b/2-data/tracking_start_times.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Jacks_WD/Spatial_learning_Monash/2-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2B5D12-A500-5945-A0F8-6F020A01BB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B64435-62B6-7E45-9680-EC0EDA5130E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{7D31A790-44E8-9F4B-9C39-D8D1C9E72198}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{7D31A790-44E8-9F4B-9C39-D8D1C9E72198}"/>
   </bookViews>
   <sheets>
     <sheet name="df4" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="551">
   <si>
     <t>unique_id</t>
   </si>
@@ -1562,9 +1562,6 @@
     <t>cam8-b3-d4-t3</t>
   </si>
   <si>
-    <t>2,4</t>
-  </si>
-  <si>
     <t>could get fish 2 by tracking separate!</t>
   </si>
   <si>
@@ -1595,9 +1592,6 @@
     <t>cam11-b3-d4-t3</t>
   </si>
   <si>
-    <t>1,2</t>
-  </si>
-  <si>
     <t>cam12-b3-d4-t1</t>
   </si>
   <si>
@@ -1623,9 +1617,6 @@
   </si>
   <si>
     <t>cam13-b3-d4-t3</t>
-  </si>
-  <si>
-    <t>maybe 2 misstart</t>
   </si>
   <si>
     <t>big play around before release</t>
@@ -2580,16 +2571,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E1" t="s">
         <v>549</v>
-      </c>
-      <c r="E1" t="s">
-        <v>552</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -3495,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="G64" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -3817,7 +3808,7 @@
       <c r="D86">
         <v>880</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>4</v>
       </c>
     </row>
@@ -3834,7 +3825,7 @@
       <c r="D87">
         <v>897</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>4</v>
       </c>
     </row>
@@ -3851,7 +3842,7 @@
       <c r="D88">
         <v>896</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>4</v>
       </c>
     </row>
@@ -3869,10 +3860,10 @@
         <v>947</v>
       </c>
       <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
         <v>4</v>
-      </c>
-      <c r="F89">
-        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
@@ -3888,7 +3879,7 @@
       <c r="D90">
         <v>848</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>4</v>
       </c>
     </row>
@@ -3905,7 +3896,7 @@
       <c r="D91">
         <v>878</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>4</v>
       </c>
     </row>
@@ -3922,7 +3913,7 @@
       <c r="D92">
         <v>1640</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>4</v>
       </c>
     </row>
@@ -3939,7 +3930,7 @@
       <c r="D93">
         <v>1758</v>
       </c>
-      <c r="E93">
+      <c r="F93">
         <v>4</v>
       </c>
     </row>
@@ -3956,13 +3947,13 @@
       <c r="D94">
         <v>2069</v>
       </c>
-      <c r="E94">
+      <c r="F94">
         <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B95">
         <v>1822</v>
@@ -3973,13 +3964,13 @@
       <c r="D95">
         <v>1841</v>
       </c>
-      <c r="E95">
+      <c r="F95">
         <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B96">
         <v>1724</v>
@@ -3990,13 +3981,13 @@
       <c r="D96">
         <v>1741</v>
       </c>
-      <c r="E96">
+      <c r="F96">
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B97">
         <v>883</v>
@@ -4007,11 +3998,11 @@
       <c r="D97">
         <v>943</v>
       </c>
-      <c r="E97">
+      <c r="F97">
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -4024,11 +4015,11 @@
       <c r="D98">
         <v>2680</v>
       </c>
-      <c r="E98">
+      <c r="F98">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -4041,11 +4032,11 @@
       <c r="D99">
         <v>1715</v>
       </c>
-      <c r="E99">
+      <c r="F99">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -4058,11 +4049,11 @@
       <c r="D100">
         <v>1651</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -4075,11 +4066,11 @@
       <c r="D101">
         <v>5469</v>
       </c>
-      <c r="E101">
+      <c r="F101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -4092,11 +4083,11 @@
       <c r="D102">
         <v>1982</v>
       </c>
-      <c r="E102">
+      <c r="F102">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -4109,11 +4100,14 @@
       <c r="D103">
         <v>1768</v>
       </c>
-      <c r="E103" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -4126,11 +4120,11 @@
       <c r="D104">
         <v>759</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -4143,11 +4137,11 @@
       <c r="D105">
         <v>754</v>
       </c>
-      <c r="E105">
+      <c r="F105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -4160,13 +4154,13 @@
       <c r="D106">
         <v>7367</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B107">
         <v>3419</v>
@@ -4177,13 +4171,16 @@
       <c r="D107">
         <v>3433</v>
       </c>
-      <c r="E107" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B108">
         <v>818</v>
@@ -4194,13 +4191,16 @@
       <c r="D108">
         <v>838</v>
       </c>
-      <c r="E108" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B109">
         <v>1178</v>
@@ -4211,11 +4211,11 @@
       <c r="D109">
         <v>1195</v>
       </c>
-      <c r="E109">
+      <c r="F109">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>106</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>107</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>108</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>2</v>
       </c>
       <c r="H134" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -4721,7 +4721,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B143">
         <v>2692</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B144">
         <v>1408</v>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B145">
         <v>2105</v>
@@ -5003,7 +5003,7 @@
         <v>4</v>
       </c>
       <c r="G161" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
@@ -5023,7 +5023,7 @@
         <v>4</v>
       </c>
       <c r="G162" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
@@ -5084,7 +5084,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B167">
         <v>2755</v>
@@ -5098,7 +5098,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B168">
         <v>2665</v>
@@ -5112,7 +5112,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B169">
         <v>1030</v>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B178">
         <v>6452</v>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B179">
         <v>1366</v>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B180">
         <v>776</v>
@@ -5324,9 +5324,6 @@
       <c r="D181">
         <v>734</v>
       </c>
-      <c r="G181" t="s">
-        <v>530</v>
-      </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
@@ -5412,7 +5409,7 @@
         <v>618</v>
       </c>
       <c r="G187" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
@@ -5445,7 +5442,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B190">
         <v>601</v>
@@ -5459,7 +5456,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B191">
         <v>566</v>
@@ -5473,7 +5470,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B192">
         <v>648</v>
@@ -5640,7 +5637,7 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B202">
         <v>1207</v>
@@ -5657,7 +5654,7 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B203">
         <v>1184</v>
@@ -5674,7 +5671,7 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B204">
         <v>436</v>
@@ -5984,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="G224" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
@@ -6003,7 +6000,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B226">
         <v>1202</v>
@@ -6017,7 +6014,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B227">
         <v>1163</v>
@@ -6034,7 +6031,7 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B228">
         <v>1295</v>
@@ -6177,7 +6174,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B238">
         <v>2213</v>
@@ -6191,7 +6188,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B239">
         <v>2164</v>
@@ -6205,7 +6202,7 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B240">
         <v>579</v>
@@ -6372,7 +6369,7 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B250">
         <v>6273</v>
@@ -6389,7 +6386,7 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B251">
         <v>1283</v>
@@ -6406,7 +6403,7 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B252">
         <v>1715</v>
@@ -6477,7 +6474,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>229</v>
       </c>
@@ -6491,7 +6488,7 @@
         <v>2939</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>230</v>
       </c>
@@ -6505,7 +6502,7 @@
         <v>2987</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>231</v>
       </c>
@@ -6519,7 +6516,7 @@
         <v>3092</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>232</v>
       </c>
@@ -6533,7 +6530,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>233</v>
       </c>
@@ -6547,7 +6544,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>234</v>
       </c>
@@ -6561,7 +6558,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>235</v>
       </c>
@@ -6575,7 +6572,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>236</v>
       </c>
@@ -6589,7 +6586,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>237</v>
       </c>
@@ -6602,8 +6599,14 @@
       <c r="D265">
         <v>2557</v>
       </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E265">
+        <v>1</v>
+      </c>
+      <c r="G265" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>238</v>
       </c>
@@ -6616,8 +6619,14 @@
       <c r="D266">
         <v>2697</v>
       </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E266">
+        <v>1</v>
+      </c>
+      <c r="G266" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>239</v>
       </c>
@@ -6630,8 +6639,14 @@
       <c r="D267">
         <v>3064</v>
       </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E267">
+        <v>1</v>
+      </c>
+      <c r="G267" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>240</v>
       </c>
@@ -6644,8 +6659,14 @@
       <c r="D268">
         <v>2110</v>
       </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E268">
+        <v>1</v>
+      </c>
+      <c r="G268" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>241</v>
       </c>
@@ -6658,8 +6679,14 @@
       <c r="D269">
         <v>3304</v>
       </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E269">
+        <v>1</v>
+      </c>
+      <c r="G269" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>242</v>
       </c>
@@ -6672,8 +6699,14 @@
       <c r="D270">
         <v>2549</v>
       </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E270">
+        <v>1</v>
+      </c>
+      <c r="G270" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>243</v>
       </c>
@@ -6686,8 +6719,14 @@
       <c r="D271">
         <v>2306</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E271">
+        <v>1</v>
+      </c>
+      <c r="G271" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>244</v>
       </c>
@@ -6700,8 +6739,14 @@
       <c r="D272">
         <v>2312</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E272">
+        <v>1</v>
+      </c>
+      <c r="G272" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>245</v>
       </c>
@@ -6714,8 +6759,14 @@
       <c r="D273">
         <v>2750</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E273">
+        <v>1</v>
+      </c>
+      <c r="G273" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>246</v>
       </c>
@@ -6728,8 +6779,14 @@
       <c r="D274">
         <v>2693</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E274">
+        <v>1</v>
+      </c>
+      <c r="G274" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>247</v>
       </c>
@@ -6742,8 +6799,14 @@
       <c r="D275">
         <v>2399</v>
       </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E275">
+        <v>1</v>
+      </c>
+      <c r="G275" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>248</v>
       </c>
@@ -6756,8 +6819,14 @@
       <c r="D276">
         <v>2600</v>
       </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E276">
+        <v>1</v>
+      </c>
+      <c r="G276" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>249</v>
       </c>
@@ -6771,7 +6840,7 @@
         <v>4260</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>250</v>
       </c>
@@ -6785,7 +6854,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>251</v>
       </c>
@@ -6799,7 +6868,7 @@
         <v>2591</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>252</v>
       </c>
@@ -6813,7 +6882,7 @@
         <v>10144</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>253</v>
       </c>
@@ -6827,7 +6896,7 @@
         <v>2848</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>254</v>
       </c>
@@ -6841,7 +6910,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>255</v>
       </c>
@@ -6855,7 +6924,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>256</v>
       </c>
@@ -6869,7 +6938,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>257</v>
       </c>
@@ -6883,7 +6952,7 @@
         <v>15372</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>258</v>
       </c>
@@ -6897,7 +6966,7 @@
         <v>6140</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>259</v>
       </c>
@@ -6911,7 +6980,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>260</v>
       </c>
@@ -6925,7 +6994,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>261</v>
       </c>
@@ -6942,7 +7011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>262</v>
       </c>
@@ -6956,7 +7025,7 @@
         <v>3077</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>263</v>
       </c>
@@ -6970,7 +7039,7 @@
         <v>3656</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>264</v>
       </c>
@@ -6984,7 +7053,7 @@
         <v>2601</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>265</v>
       </c>
@@ -6998,7 +7067,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>266</v>
       </c>
@@ -7012,7 +7081,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>267</v>
       </c>
@@ -7026,7 +7095,7 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>268</v>
       </c>
@@ -7040,7 +7109,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>269</v>
       </c>
@@ -7054,7 +7123,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>270</v>
       </c>
@@ -7068,7 +7137,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>271</v>
       </c>
@@ -7082,7 +7151,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>272</v>
       </c>
@@ -7096,7 +7165,7 @@
         <v>2682</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>273</v>
       </c>
@@ -7113,7 +7182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>274</v>
       </c>
@@ -7132,11 +7201,8 @@
       <c r="F302">
         <v>1</v>
       </c>
-      <c r="G302">
-        <v>30672</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>275</v>
       </c>
@@ -7153,7 +7219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>276</v>
       </c>
@@ -7187,7 +7253,7 @@
         <v>1</v>
       </c>
       <c r="G305" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -8563,7 +8629,7 @@
         <v>2366</v>
       </c>
       <c r="E393" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G393" t="s">
         <v>367</v>
@@ -8628,7 +8694,7 @@
         <v>4</v>
       </c>
       <c r="G397" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.2">
@@ -10481,7 +10547,7 @@
       <c r="D526">
         <v>3000</v>
       </c>
-      <c r="E526">
+      <c r="F526">
         <v>4</v>
       </c>
     </row>
@@ -10498,11 +10564,14 @@
       <c r="D527">
         <v>2113</v>
       </c>
-      <c r="E527" t="s">
+      <c r="E527">
+        <v>2</v>
+      </c>
+      <c r="F527">
+        <v>4</v>
+      </c>
+      <c r="G527" t="s">
         <v>509</v>
-      </c>
-      <c r="G527" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.2">
@@ -10518,11 +10587,11 @@
       <c r="D528">
         <v>1807</v>
       </c>
-      <c r="E528">
+      <c r="F528">
         <v>4</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>491</v>
       </c>
@@ -10535,11 +10604,11 @@
       <c r="D529">
         <v>5674</v>
       </c>
-      <c r="E529">
+      <c r="F529">
         <v>4</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>492</v>
       </c>
@@ -10552,11 +10621,11 @@
       <c r="D530">
         <v>2116</v>
       </c>
-      <c r="E530">
+      <c r="F530">
         <v>4</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>493</v>
       </c>
@@ -10569,11 +10638,11 @@
       <c r="D531">
         <v>1934</v>
       </c>
-      <c r="E531">
+      <c r="F531">
         <v>4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>494</v>
       </c>
@@ -10586,11 +10655,11 @@
       <c r="D532">
         <v>954</v>
       </c>
-      <c r="E532">
+      <c r="F532">
         <v>4</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>495</v>
       </c>
@@ -10603,11 +10672,11 @@
       <c r="D533">
         <v>967</v>
       </c>
-      <c r="E533">
+      <c r="F533">
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>496</v>
       </c>
@@ -10620,13 +10689,13 @@
       <c r="D534">
         <v>7610</v>
       </c>
-      <c r="E534">
+      <c r="F534">
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B535">
         <v>3499</v>
@@ -10637,13 +10706,13 @@
       <c r="D535">
         <v>3670</v>
       </c>
-      <c r="E535">
+      <c r="F535">
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B536">
         <v>895</v>
@@ -10654,13 +10723,13 @@
       <c r="D536">
         <v>1022</v>
       </c>
-      <c r="E536">
+      <c r="F536">
         <v>4</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B537">
         <v>1292</v>
@@ -10671,7 +10740,7 @@
       <c r="D537">
         <v>1458</v>
       </c>
-      <c r="E537">
+      <c r="F537">
         <v>4</v>
       </c>
     </row>
